--- a/booking_forms/022_hotel_booking_quotation_form--booking_forms.xlsx
+++ b/booking_forms/022_hotel_booking_quotation_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'checkin',_'label':_'checkin',_'value':_'checkin'}</t>
+          <t>checkin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'checkin', 'label': 'Checkin', 'value': 'checkin'}</t>
+          <t>Checkin</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'checkout',_'label':_'checkout',_'value':_'checkout'}</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'checkout', 'label': 'Checkout', 'value': 'checkout'}</t>
+          <t>Checkout</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'arrival_date',_'label':_'arrival_date',_'value':_'arrival_date'}</t>
+          <t>arrival_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'arrival_date', 'label': 'Arrival Date', 'value': 'arrival_date'}</t>
+          <t>Arrival Date</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'departure_date',_'label':_'departure_date',_'value':_'departure_date'}</t>
+          <t>departure_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'departure_date', 'label': 'Departure Date', 'value': 'departure_date'}</t>
+          <t>Departure Date</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'hint':_'describe_other_requests'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other', 'hint': 'Describe other requests'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'double',_'label':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'double', 'label': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'suite',_'label':_'suite'}</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'suite', 'label': 'Suite'}</t>
+          <t>Suite</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other',_'hint':_'specify_other_type_of_accommodation'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other', 'hint': 'Specify other type of accommodation'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'net',_'label':_'net'}</t>
+          <t>net</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'net', 'label': 'Net'}</t>
+          <t>Net</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'vat',_'label':_'vat'}</t>
+          <t>vat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'vat', 'label': 'Vat'}</t>
+          <t>Vat</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'hint':_'specify_other_payment_terms'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other', 'hint': 'Specify other payment terms'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
